--- a/produits/preuves/sortie/c7-facture-piege/c7-facture-piege.xlsx
+++ b/produits/preuves/sortie/c7-facture-piege/c7-facture-piege.xlsx
@@ -262,6 +262,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
